--- a/data/WP18/WP18_sachgebiete_AfD.xlsx
+++ b/data/WP18/WP18_sachgebiete_AfD.xlsx
@@ -3546,13 +3546,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D0BE86A-2C1B-43AF-8B25-546DAE7F652F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{722FCD0A-1E43-4AFD-AD4E-95D0DB3A6BE7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB8F8115-FC14-4615-BD78-89B16960498C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD4719D-66DA-4D49-A691-7A43F2D79C5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C54747A3-77B9-4484-8A79-F953AA4AFBFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D94DE46-23ED-4384-AD8F-85456327FB39}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_AfD.xlsx
+++ b/data/WP18/WP18_sachgebiete_AfD.xlsx
@@ -446,7 +446,7 @@
         <v>36.7064156206416</v>
       </c>
       <c r="E2" t="n">
-        <v>1091</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>38.7853577371048</v>
       </c>
       <c r="E3" t="n">
-        <v>493</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>34.8965517241379</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>35.7095435684647</v>
       </c>
       <c r="E5" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>36.5492957746479</v>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>34.7358490566038</v>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         <v>37.8366013071895</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>34.6862745098039</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>32.0958904109589</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>35.2887323943662</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
@@ -616,7 +616,7 @@
         <v>37.0618556701031</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>36.3086419753086</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         <v>34.1973684210526</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>34.28</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>33.3285714285714</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -752,7 +752,7 @@
         <v>33.9032258064516</v>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>35.0188679245283</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5370129-3D6C-4687-856A-9BA2BB28D8E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B94590C-A088-4D5D-8B75-BCDB9749F9C9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28F2107D-5845-430D-ADBB-E20CD001022C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE3DF34F-D278-4301-B623-8096D221332B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7244D90A-8CC9-472F-99DA-CCB31D5A21EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ABBE856-8497-4683-AFFC-D4C886838268}"/>
 </file>